--- a/decision_tree_dataset.xlsx
+++ b/decision_tree_dataset.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sparta\OneDrive\Desktop\Machine Learning\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA63D772-D967-49AD-8CD7-C4881E36026D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1DD8E1A-6BA8-41B0-B97B-F387BC3B28FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
